--- a/themes/refinancing.xlsx
+++ b/themes/refinancing.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -470,141 +470,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование автокредита можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie)   </t>
+          <t xml:space="preserve">    • Сумма кредита: для Москвы, Санкт-Петербурга и Московской области - от 900 000 до 20 000 000 рублей, для Сочи - 12 000 000 рублей, для других городов - 9 000 000 рублей.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование автокредита можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie).   </t>
+          <t xml:space="preserve">    • Сумма кредита: для Москвы, Санкт-Петербурга и Московской области — от 900 000 до 20 000 000 рублей, для Сочи — 12 000 000 рублей, для других городов — 9 000 000 рублей.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Понял вас. Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке](https://uralsib.ru/kredity/kredit-na-lyubye-tseli?utm_source=chatbot) </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Понял вас. Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке](https://uralsib.ru/kredity/kredit-na-lyubye-tseli?utm_source=chatbot). </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование кредитной карты можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie)       </t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование кредитной карты можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie).       </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Понял вас. Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке](https://uralsib.ru/kredity/kredit-na-lyubye-tseli?utm_source=chatbot)   </t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Понял вас. Более подробные условия и ответы на часто задаваемые вопросы вы сможете найти по [ссылке](https://uralsib.ru/kredity/kredit-na-lyubye-tseli?utm_source=chatbot).   </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>90</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Сумма кредита: для Москвы, Санкт-Петербурга и Московской области - от 900 000 до 20 000 000 рублей, для Сочи - 12 000 000 рублей, для других городов - 9 000 000 рублей.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • Сумма кредита: для Москвы, Санкт-Петербурга и Московской области — от 900 000 до 20 000 000 рублей, для Сочи — 12 000 000 рублей, для других городов — 9 000 000 рублей.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>дефисы заменены на тире (трижды)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>93</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Заявку можно подать в отделении банка, либо на [сайте](https://uralsib.ru/ipoteka/refinansirovanie)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Заявку можно подать в отделении банка, либо на [сайте](https://uralsib.ru/ipoteka/refinansirovanie).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>107</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование потребительского кредита можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Узнать условия и оставить заявку на рефинансирование потребительского кредита можно по [ссылке](https://uralsib.ru/kredity/refinansirovanie).</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
